--- a/stories/arbres/ATOM-LAN.SON.001-01.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Iris s'assoit près de la fenêtre. Papa est là. Il pleut. Ça fait plic ploc. Papa dit : c'est un son. Quel nom ? Iris dit : la pluie. Papa dit : oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Papa dit : encore un son. Quel nom ? Iris dit : le train. Papa dit : oui. Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou. Papa dit : un son. Quel nom ? Iris dit : le chat. Le chat vient. Iris le caresse. Pluie. Train. Chat. On entend. On nomme le son.</t>
+          <t>Iris s'assoit près de la fenêtre. Papa est là. Il pleut. Ça fait plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou. Un son. Quel nom ? Le chat. Le chat vient. Iris le caresse. Pluie. Train. Chat. On entend. On nomme le son.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,22 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Iris s'assoit près de la fenêtre. Papa est là. Il pleut. Ça fait plic ploc.
+papa|C'est un son. Quel nom ?
+enfant-f|La pluie.
+papa|Oui.
+narrateur|Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou.
+papa|Encore un son. Quel nom ?
+enfant-f|Le train.
+papa|Oui.
+narrateur|Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou.
+papa|Un son. Quel nom ?
+enfant-f|Le chat.
+narrateur|Le chat vient. Iris le caresse. Pluie. Train. Chat. On entend. On nomme le son.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Iris entend un bruit. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Iris a entendu un son. Elle a dit le nom. Pluie. Train. Chat.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1833,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat ronronne. Iris pose la tête sur papa.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +2000,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-01.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1321,6 +1326,7 @@
 narrateur|Le chat vient. Iris le caresse. Pluie. Train. Chat. On entend. On nomme le son.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1510,7 @@
           <t>narrateur|Iris entend un bruit. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1682,7 @@
           <t>narrateur|Iris a entendu un son. Elle a dit le nom. Pluie. Train. Chat.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1846,7 @@
           <t>narrateur|Le chat ronronne. Iris pose la tête sur papa.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.SON.001-01.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Iris nomme les sons</t>
+          <t>Le doudou et la pluie de Nina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le doudou gris attend sur le rebord. Nina écoute la pluie, le train, le chat. Elle dit le nom de chaque son.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Iris s'assoit près de la fenêtre. Papa est là. Il pleut. Ça fait plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou. Un son. Quel nom ? Le chat. Le chat vient. Iris le caresse. Pluie. Train. Chat. On entend. On nomme le son.</t>
+          <t>Un doudou gris attend sur le rebord. La pluie tape le verre. Ça fait plic ploc. La couverture est encore chaude. Ça sent le linge propre. Papa plie un pull. Le pull est bleu, un peu rêche. Une chaussette a glissé au sol. Le plancher est frais sous les pieds. Tu entends ça, Nina ? Oui, papa. Plic ploc. Je prépare le cacao. Je vous écoute. En ce moment, Nina s'assoit. Elle prend le doudou. Le doudou est doux. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. Le chat vient. Nina le caresse. Le poil est chaud. Pluie. Train. Chat. On entend. On nomme le son. Pluie. Train. Chat. Bravo, Nina. C'est du bon travail. Tu as dit le nom. Tu as fini d'écouter ? Encore un peu. D'accord. Nina serre le doudou. Une goutte descend sur la vitre. Elle brille, puis elle file. Encore la pluie. Plic ploc. Tu as nommé le son.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Iris s'assoit près de la fenêtre. Papa est là. Il pleut. Ça fait plic ploc.
-papa|C'est un son. Quel nom ?
+          <t>narrateur|Un doudou gris attend sur le rebord.
+narrateur|La pluie tape le verre.
+narrateur|Ça fait plic ploc.
+narrateur|La couverture est encore chaude.
+narrateur|Ça sent le linge propre.
+narrateur|Papa plie un pull.
+narrateur|Le pull est bleu, un peu rêche.
+narrateur|Une chaussette a glissé au sol.
+narrateur|Le plancher est frais sous les pieds.
+papa|Tu entends ça, Nina ?
+enfant-f|Oui, papa.
+enfant-f|Plic ploc.
+maman|Je prépare le cacao.
+maman|Je vous écoute.
+narrateur|En ce moment, Nina s'assoit.
+narrateur|Elle prend le doudou.
+narrateur|Le doudou est doux.
+papa|C'est un son.
+papa|Quel nom ?
 enfant-f|La pluie.
 papa|Oui.
-narrateur|Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou.
-papa|Encore un son. Quel nom ?
+papa|Le nom du son, c'est la pluie.
+narrateur|Plus loin, un bruit long.
+narrateur|Tchou tchou.
+papa|Encore un son.
+papa|Quel nom ?
 enfant-f|Le train.
 papa|Oui.
-narrateur|Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou.
-papa|Un son. Quel nom ?
+papa|Le nom du son, c'est le train.
+narrateur|Puis, dans la pièce, un miaulement.
+narrateur|Miaou.
+papa|Un son.
+papa|Quel nom ?
 enfant-f|Le chat.
-narrateur|Le chat vient. Iris le caresse. Pluie. Train. Chat. On entend. On nomme le son.</t>
+papa|Oui.
+narrateur|Le chat vient.
+narrateur|Nina le caresse.
+narrateur|Le poil est chaud.
+maman|Pluie.
+maman|Train.
+maman|Chat.
+papa|On entend.
+papa|On nomme le son.
+enfant-f|Pluie.
+enfant-f|Train.
+enfant-f|Chat.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+maman|Tu as dit le nom.
+papa|Tu as fini d'écouter ?
+enfant-f|Encore un peu.
+papa|D'accord.
+narrateur|Nina serre le doudou.
+narrateur|Une goutte descend sur la vitre.
+narrateur|Elle brille, puis elle file.
+papa|Encore la pluie.
+enfant-f|Plic ploc.
+maman|Tu as nommé le son.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1351,7 +1409,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Iris entend un bruit. C'est quoi ?</t>
+          <t>Nina entend un bruit. C'est quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,7 +1565,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Iris entend un bruit. C'est quoi ?</t>
+          <t>narrateur|Nina entend un bruit.
+narrateur|C'est quoi ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1535,7 +1594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Iris a entendu un son. Elle a dit le nom. Pluie. Train. Chat.</t>
+          <t>Nina a entendu un son. Elle a dit le nom. Pluie. Train. Chat. Bravo. Tu as nommé le son. C'est du bon travail, Nina. Le chat est là. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1679,7 +1738,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Iris a entendu un son. Elle a dit le nom. Pluie. Train. Chat.</t>
+          <t>narrateur|Nina a entendu un son.
+narrateur|Elle a dit le nom.
+papa|Pluie.
+papa|Train.
+papa|Chat.
+papa|Bravo.
+maman|Tu as nommé le son.
+maman|C'est du bon travail, Nina.
+enfant-f|Le chat est là.
+papa|Oui.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1707,7 +1775,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le chat ronronne. Iris pose la tête sur papa.</t>
+          <t>Le chat ronronne. C'est un petit son. Quel nom, celui-là ? Le chat. Oui. On nomme le son. Nina pose la tête sur papa. Le doudou reste sur ses genoux. Le pull bleu est plié, maintenant. Le cacao est chaud. Tu viens ? Oui, maman. La chaussette attend encore au sol.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1843,7 +1911,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le chat ronronne. Iris pose la tête sur papa.</t>
+          <t>narrateur|Le chat ronronne.
+narrateur|C'est un petit son.
+papa|Quel nom, celui-là ?
+enfant-f|Le chat.
+papa|Oui.
+papa|On nomme le son.
+narrateur|Nina pose la tête sur papa.
+narrateur|Le doudou reste sur ses genoux.
+narrateur|Le pull bleu est plié, maintenant.
+maman|Le cacao est chaud.
+maman|Tu viens ?
+enfant-f|Oui, maman.
+narrateur|La chaussette attend encore au sol.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1871,7 +1951,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Nina. Tu as fait du bon travail. Le doudou reste sur le rebord. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2011,7 +2091,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai entendu un son.
+enfant-f|J'ai dit le nom.
+papa|Bravo, Nina.
+maman|Tu as fait du bon travail.
+narrateur|Le doudou reste sur le rebord.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2033,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2156,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-01.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un doudou gris attend sur le rebord. La pluie tape le verre. Ça fait plic ploc. La couverture est encore chaude. Ça sent le linge propre. Papa plie un pull. Le pull est bleu, un peu rêche. Une chaussette a glissé au sol. Le plancher est frais sous les pieds. Tu entends ça, Nina ? Oui, papa. Plic ploc. Je prépare le cacao. Je vous écoute. En ce moment, Nina s'assoit. Elle prend le doudou. Le doudou est doux. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. Le chat vient. Nina le caresse. Le poil est chaud. Pluie. Train. Chat. On entend. On nomme le son. Pluie. Train. Chat. Bravo, Nina. C'est du bon travail. Tu as dit le nom. Tu as fini d'écouter ? Encore un peu. D'accord. Nina serre le doudou. Une goutte descend sur la vitre. Elle brille, puis elle file. Encore la pluie. Plic ploc. Tu as nommé le son.</t>
+          <t>Un doudou gris attend sur le rebord. La pluie tape le verre. Ça fait plic ploc. La couverture est encore chaude. Ça sent le linge propre. Papa plie un pull. Le pull est bleu, un peu rêche. Une chaussette a glissé au sol. Le plancher est frais sous les pieds. Tu entends ça, Nina ? Oui, papa. Plic ploc. Je prépare le cacao. Je vous écoute. En ce moment, Nina s'assoit. Elle prend le doudou. Le doudou est doux. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. Le chat vient. Nina le caresse. Le poil est chaud. Pluie. Train. Chat. On entend. On nomme le son. Pluie. Train. Chat. Bravo, Nina. Tu as dit le nom. Tu as fini d'écouter ? Encore un peu. D'accord. Nina serre le doudou. Une goutte descend sur la vitre. Elle brille, puis elle file. Encore la pluie. Plic ploc. Tu as nommé le son.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Iris s'assoit près de la fenêtre. Papa est là. Il pleut. Ça fait plic ploc. Papa dit : c'est un &lt;emphasis level="moderate"&gt;son&lt;/emphasis&gt;. Quel nom ? Iris dit : la pluie. Papa dit : oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Papa dit : encore un son. Quel nom ? Iris dit : le train. Papa dit : oui. Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou. Papa dit : un son. Quel nom ? Iris dit : le chat. Le chat vient. Iris le caresse. Pluie. Train. Chat. On entend. On nomme le son.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un doudou gris attend sur le rebord. La pluie tape le verre. Ça fait plic ploc. La couverture est encore chaude. Ça sent le linge propre. Papa plie un pull. Le pull est bleu, un peu rêche. Une chaussette a glissé au sol. Le plancher est frais sous les pieds. Tu entends ça, Nina ? Oui, papa. Plic ploc. Je prépare le cacao. Je vous écoute. En ce moment, Nina s'assoit. Elle prend le doudou. Le doudou est doux. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. Le chat vient. Nina le caresse. Le poil est chaud. Pluie. Train. Chat. On entend. On nomme le son. Pluie. Train. Chat. Bravo, Nina. Tu as dit le nom. Tu as fini d'écouter ? Encore un peu. D'accord. Nina serre le doudou. Une goutte descend sur la vitre. Elle brille, puis elle file. Encore la pluie. Plic ploc. Tu as nommé le son.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1371,7 +1371,6 @@
 enfant-f|Train.
 enfant-f|Chat.
 papa|Bravo, Nina.
-papa|C'est du bon travail.
 maman|Tu as dit le nom.
 papa|Tu as fini d'écouter ?
 enfant-f|Encore un peu.
@@ -1384,7 +1383,6 @@
 maman|Tu as nommé le son.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1414,7 +1412,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Iris entend un bruit. C'est quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina entend un bruit. C'est quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1569,7 +1567,6 @@
 narrateur|C'est quoi ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1594,12 +1591,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a entendu un son. Elle a dit le nom. Pluie. Train. Chat. Bravo. Tu as nommé le son. C'est du bon travail, Nina. Le chat est là. Oui.</t>
+          <t>Nina a entendu un son. Elle a dit le nom. Pluie. Train. Chat. Bravo. Tu as nommé le son. Le chat est là. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Iris a entendu un &lt;emphasis level="moderate"&gt;son&lt;/emphasis&gt;. Elle a dit le nom. Pluie. Train. Chat.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a entendu un son. Elle a dit le nom. Pluie. Train. Chat. Bravo. Tu as nommé le son. Le chat est là. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1745,12 +1742,10 @@
 papa|Chat.
 papa|Bravo.
 maman|Tu as nommé le son.
-maman|C'est du bon travail, Nina.
 enfant-f|Le chat est là.
 papa|Oui.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1780,7 +1775,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le chat ronronne. Iris pose la tête sur papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le chat ronronne. C'est un petit son. Quel nom, celui-là ? Le chat. Oui. On nomme le son. Nina pose la tête sur papa. Le doudou reste sur ses genoux. Le pull bleu est plié, maintenant. Le cacao est chaud. Tu viens ? Oui, maman. La chaussette attend encore au sol.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1926,7 +1921,6 @@
 narrateur|La chaussette attend encore au sol.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1951,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Nina. Tu as fait du bon travail. Le doudou reste sur le rebord. L'histoire est finie.</t>
+          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Nina. Le doudou reste sur le rebord.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Nina. Le doudou reste sur le rebord.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2094,12 +2088,9 @@
           <t>enfant-f|J'ai entendu un son.
 enfant-f|J'ai dit le nom.
 papa|Bravo, Nina.
-maman|Tu as fait du bon travail.
-narrateur|Le doudou reste sur le rebord.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le doudou reste sur le rebord.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2118,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2163,6 +2154,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-01.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-01.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Iris, papa</t>
+          <t>Nina, papa, maman</t>
         </is>
       </c>
     </row>
